--- a/feedback_forms/012_student_leadership_teacher_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/012_student_leadership_teacher_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>demonstrates_initiative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>Demonstrates</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>leadership_quality_1</t>
+          <t>leads_others</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Demonstrates</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>leadership_quality_2</t>
+          <t>takes_responsibility</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Takes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,63 +630,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>initiative_takes</t>
+          <t>comments_on_student</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Takes</t>
+          <t>Comments on Student</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>leadership_quality_3</t>
+          <t>teacher_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Comments on Teacher</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>responsibility_takes</t>
+          <t>student_leadership_trend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Takes</t>
+          <t>Student Leadership Trend</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,391 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>leadership_quality_4</t>
+          <t>comments_on_teacher</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Demonstrates</t>
+          <t>Comments on Teacher (2)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>student_leadership_trend</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Student Leadership Trend</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>teacher_comments</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Teacher Comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>teacher_name</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>student_comments</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Student Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>student_leadership_trend_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Student Leadership Trend</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>teacher_name_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>teacher_comments</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Teacher Comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>student_leadership_trend_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Student Leadership Trend</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>teacher_name_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>teacher_comments_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Teacher Comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>student_leadership_trend_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Student Leadership Trend</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>teacher_name_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>teacher_comments_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Teacher Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>student_id_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teacher_name_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +730,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +758,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>leadership_quality_1_choices</t>
+          <t>demonstrates_initiative_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +775,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>leadership_quality_1_choices</t>
+          <t>demonstrates_initiative_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>leadership_quality_1_choices</t>
+          <t>demonstrates_initiative_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +809,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>leadership_quality_1_choices</t>
+          <t>demonstrates_initiative_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +826,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>leadership_quality_1_choices</t>
+          <t>demonstrates_initiative_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +843,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>leadership_quality_2_choices</t>
+          <t>leads_others_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>leadership_quality_2_choices</t>
+          <t>leads_others_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +877,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>leadership_quality_2_choices</t>
+          <t>leads_others_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +894,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>leadership_quality_2_choices</t>
+          <t>leads_others_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +911,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>leadership_quality_2_choices</t>
+          <t>leads_others_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,338 +928,100 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>initiative_takes_choices</t>
+          <t>leads_others_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Strongly Agree</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>initiative_takes_choices</t>
+          <t>takes_responsibility_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Somewhat Agree</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>initiative_takes_choices</t>
+          <t>takes_responsibility_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>initiative_takes_choices</t>
+          <t>takes_responsibility_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>somewhat_disagree</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Somewhat Disagree</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>initiative_takes_choices</t>
+          <t>takes_responsibility_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>strongly_disagree</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Strongly Disagree</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>leadership_quality_3_choices</t>
+          <t>takes_responsibility_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>leadership_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>leadership_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>leadership_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>leadership_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>responsibility_takes_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>responsibility_takes_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>responsibility_takes_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>responsibility_takes_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>responsibility_takes_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>leadership_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>leadership_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>leadership_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>leadership_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>leadership_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Strongly Disagree</t>
         </is>
